--- a/results/test/binary_AD_results.xlsx
+++ b/results/test/binary_AD_results.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,70 +455,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -531,54 +496,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.746</v>
+        <v>0.71205</v>
       </c>
       <c r="C2" t="n">
-        <v>0.666</v>
+        <v>0.63335</v>
       </c>
       <c r="D2" t="n">
-        <v>0.848</v>
+        <v>0.81308</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8</v>
+        <v>0.875</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.61538</v>
       </c>
       <c r="I2" t="n">
-        <v>0.756</v>
+        <v>0.77778</v>
       </c>
       <c r="J2" t="n">
-        <v>0.875</v>
+        <v>0.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="R2" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -589,54 +533,33 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.763</v>
+        <v>0.72395</v>
       </c>
       <c r="C3" t="n">
-        <v>0.698</v>
+        <v>0.66499</v>
       </c>
       <c r="D3" t="n">
-        <v>0.841</v>
+        <v>0.79439</v>
       </c>
       <c r="E3" t="n">
-        <v>0.822</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.822</v>
+        <v>0.9375</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.77778</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.723</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="R3" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -647,54 +570,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.724</v>
+        <v>0.67414</v>
       </c>
       <c r="C4" t="n">
-        <v>0.636</v>
+        <v>0.5805399999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.841</v>
+        <v>0.80374</v>
       </c>
       <c r="E4" t="n">
-        <v>0.777</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.777</v>
+        <v>0.8125</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.61538</v>
       </c>
       <c r="I4" t="n">
-        <v>0.713</v>
+        <v>0.77778</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="R4" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -705,54 +607,33 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.742</v>
+        <v>0.71567</v>
       </c>
       <c r="C5" t="n">
-        <v>0.664</v>
+        <v>0.6511400000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.841</v>
+        <v>0.79439</v>
       </c>
       <c r="E5" t="n">
-        <v>0.798</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.798</v>
+        <v>0.9375</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.777</v>
+        <v>0.77778</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="R5" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -767,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,70 +674,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -869,55 +715,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.704</v>
+        <v>0.6732900000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.666</v>
+        <v>0.63335</v>
       </c>
       <c r="D2" t="n">
-        <v>0.745</v>
+        <v>0.7186</v>
       </c>
       <c r="E2" t="n">
-        <v>0.787</v>
+        <v>0.96348</v>
       </c>
       <c r="F2" t="n">
-        <v>0.961</v>
+        <v>0.97502</v>
       </c>
       <c r="G2" t="n">
-        <v>0.792</v>
+        <v>0.71119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.975</v>
+        <v>0.52584</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.64444</v>
       </c>
       <c r="J2" t="n">
-        <v>0.711</v>
+        <v>0.57325</v>
       </c>
       <c r="K2" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.554</v>
+        <v>0.55405</v>
       </c>
     </row>
     <row r="3">
@@ -927,55 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.71</v>
+        <v>0.67536</v>
       </c>
       <c r="C3" t="n">
-        <v>0.698</v>
+        <v>0.66499</v>
       </c>
       <c r="D3" t="n">
-        <v>0.722</v>
+        <v>0.68607</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.96196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.958</v>
+        <v>0.96363</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.73939</v>
       </c>
       <c r="H3" t="n">
-        <v>0.964</v>
+        <v>0.40055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.718</v>
+        <v>0.6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.739</v>
+        <v>0.5539500000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5583</v>
       </c>
     </row>
     <row r="4">
@@ -985,55 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.676</v>
+        <v>0.63648</v>
       </c>
       <c r="C4" t="n">
-        <v>0.636</v>
+        <v>0.5805399999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.722</v>
+        <v>0.70435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.765</v>
+        <v>0.96146</v>
       </c>
       <c r="F4" t="n">
-        <v>0.96</v>
+        <v>0.89315</v>
       </c>
       <c r="G4" t="n">
-        <v>0.743</v>
+        <v>0.68428</v>
       </c>
       <c r="H4" t="n">
-        <v>0.893</v>
+        <v>0.51189</v>
       </c>
       <c r="I4" t="n">
-        <v>0.659</v>
+        <v>0.64444</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.544</v>
+        <v>0.54426</v>
       </c>
     </row>
     <row r="5">
@@ -1043,55 +826,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.681</v>
+        <v>0.6621899999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.664</v>
+        <v>0.6511400000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.699</v>
+        <v>0.67362</v>
       </c>
       <c r="E5" t="n">
-        <v>0.784</v>
+        <v>0.96178</v>
       </c>
       <c r="F5" t="n">
-        <v>0.956</v>
+        <v>0.8854300000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.759</v>
+        <v>0.72435</v>
       </c>
       <c r="H5" t="n">
-        <v>0.885</v>
+        <v>0.38616</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.724</v>
+        <v>0.5538</v>
       </c>
       <c r="K5" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.542</v>
+        <v>0.54195</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,70 +893,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -1207,55 +934,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.655</v>
+        <v>0.6291</v>
       </c>
       <c r="C2" t="n">
-        <v>0.666</v>
+        <v>0.63335</v>
       </c>
       <c r="D2" t="n">
-        <v>0.644</v>
+        <v>0.6249</v>
       </c>
       <c r="E2" t="n">
-        <v>0.756</v>
+        <v>0.8508599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.874</v>
+        <v>0.84379</v>
       </c>
       <c r="G2" t="n">
-        <v>0.745</v>
+        <v>0.64684</v>
       </c>
       <c r="H2" t="n">
-        <v>0.844</v>
+        <v>0.43641</v>
       </c>
       <c r="I2" t="n">
-        <v>0.656</v>
+        <v>0.56825</v>
       </c>
       <c r="J2" t="n">
-        <v>0.647</v>
+        <v>0.47102</v>
       </c>
       <c r="K2" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.476</v>
+        <v>0.47619</v>
       </c>
     </row>
     <row r="3">
@@ -1265,55 +971,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.651</v>
+        <v>0.61991</v>
       </c>
       <c r="C3" t="n">
-        <v>0.698</v>
+        <v>0.66499</v>
       </c>
       <c r="D3" t="n">
-        <v>0.611</v>
+        <v>0.58056</v>
       </c>
       <c r="E3" t="n">
-        <v>0.762</v>
+        <v>0.81337</v>
       </c>
       <c r="F3" t="n">
-        <v>0.839</v>
+        <v>0.81892</v>
       </c>
       <c r="G3" t="n">
-        <v>0.753</v>
+        <v>0.66468</v>
       </c>
       <c r="H3" t="n">
-        <v>0.819</v>
+        <v>0.31366</v>
       </c>
       <c r="I3" t="n">
-        <v>0.681</v>
+        <v>0.5555600000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.665</v>
+        <v>0.44685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.454</v>
+        <v>0.45413</v>
       </c>
     </row>
     <row r="4">
@@ -1323,55 +1008,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.643</v>
+        <v>0.61089</v>
       </c>
       <c r="C4" t="n">
-        <v>0.636</v>
+        <v>0.5805399999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.65</v>
+        <v>0.6446</v>
       </c>
       <c r="E4" t="n">
-        <v>0.753</v>
+        <v>0.9248</v>
       </c>
       <c r="F4" t="n">
-        <v>0.922</v>
+        <v>0.81978</v>
       </c>
       <c r="G4" t="n">
-        <v>0.716</v>
+        <v>0.62295</v>
       </c>
       <c r="H4" t="n">
-        <v>0.82</v>
+        <v>0.44074</v>
       </c>
       <c r="I4" t="n">
-        <v>0.629</v>
+        <v>0.56825</v>
       </c>
       <c r="J4" t="n">
-        <v>0.623</v>
+        <v>0.49686</v>
       </c>
       <c r="K4" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.49</v>
+        <v>0.49049</v>
       </c>
     </row>
     <row r="5">
@@ -1381,55 +1045,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.641</v>
+        <v>0.6291099999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.664</v>
+        <v>0.6511400000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.62</v>
+        <v>0.60853</v>
       </c>
       <c r="E5" t="n">
-        <v>0.765</v>
+        <v>0.9142400000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.902</v>
+        <v>0.79247</v>
       </c>
       <c r="G5" t="n">
-        <v>0.723</v>
+        <v>0.6491</v>
       </c>
       <c r="H5" t="n">
-        <v>0.792</v>
+        <v>0.316</v>
       </c>
       <c r="I5" t="n">
-        <v>0.656</v>
+        <v>0.5555600000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.649</v>
+        <v>0.47278</v>
       </c>
       <c r="K5" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.472</v>
+        <v>0.47233</v>
       </c>
     </row>
   </sheetData>
@@ -1443,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1469,70 +1112,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -1545,55 +1153,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.522</v>
+        <v>0.52117</v>
       </c>
       <c r="C2" t="n">
-        <v>0.613</v>
+        <v>0.61131</v>
       </c>
       <c r="D2" t="n">
-        <v>0.454</v>
+        <v>0.45419</v>
       </c>
       <c r="E2" t="n">
-        <v>0.648</v>
+        <v>0.57536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.38493</v>
       </c>
       <c r="G2" t="n">
-        <v>0.473</v>
+        <v>0.4655</v>
       </c>
       <c r="H2" t="n">
-        <v>0.385</v>
+        <v>0.3621</v>
       </c>
       <c r="I2" t="n">
-        <v>0.529</v>
+        <v>0.56825</v>
       </c>
       <c r="J2" t="n">
-        <v>0.465</v>
+        <v>0.40254</v>
       </c>
       <c r="K2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.322</v>
+        <v>0.32161</v>
       </c>
     </row>
     <row r="3">
@@ -1603,55 +1190,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.522</v>
+        <v>0.51785</v>
       </c>
       <c r="C3" t="n">
-        <v>0.645</v>
+        <v>0.64273</v>
       </c>
       <c r="D3" t="n">
-        <v>0.439</v>
+        <v>0.43361</v>
       </c>
       <c r="E3" t="n">
-        <v>0.658</v>
+        <v>0.55687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.672</v>
+        <v>0.36527</v>
       </c>
       <c r="G3" t="n">
-        <v>0.466</v>
+        <v>0.58518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.365</v>
+        <v>0.25469</v>
       </c>
       <c r="I3" t="n">
-        <v>0.614</v>
+        <v>0.5555600000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.585</v>
+        <v>0.37832</v>
       </c>
       <c r="K3" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.292</v>
+        <v>0.29217</v>
       </c>
     </row>
     <row r="4">
@@ -1661,55 +1227,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.598</v>
+        <v>0.57369</v>
       </c>
       <c r="C4" t="n">
-        <v>0.583</v>
+        <v>0.54815</v>
       </c>
       <c r="D4" t="n">
-        <v>0.613</v>
+        <v>0.60172</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>0.8688</v>
       </c>
       <c r="F4" t="n">
-        <v>0.877</v>
+        <v>0.78921</v>
       </c>
       <c r="G4" t="n">
-        <v>0.67</v>
+        <v>0.57014</v>
       </c>
       <c r="H4" t="n">
-        <v>0.789</v>
+        <v>0.40375</v>
       </c>
       <c r="I4" t="n">
-        <v>0.576</v>
+        <v>0.56825</v>
       </c>
       <c r="J4" t="n">
-        <v>0.57</v>
+        <v>0.40254</v>
       </c>
       <c r="K4" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.49</v>
+        <v>0.49049</v>
       </c>
     </row>
     <row r="5">
@@ -1719,55 +1264,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.594</v>
+        <v>0.59193</v>
       </c>
       <c r="C5" t="n">
-        <v>0.609</v>
+        <v>0.61831</v>
       </c>
       <c r="D5" t="n">
-        <v>0.581</v>
+        <v>0.5677</v>
       </c>
       <c r="E5" t="n">
-        <v>0.712</v>
+        <v>0.85977</v>
       </c>
       <c r="F5" t="n">
-        <v>0.858</v>
+        <v>0.7621</v>
       </c>
       <c r="G5" t="n">
-        <v>0.677</v>
+        <v>0.61642</v>
       </c>
       <c r="H5" t="n">
-        <v>0.762</v>
+        <v>0.29439</v>
       </c>
       <c r="I5" t="n">
-        <v>0.613</v>
+        <v>0.5555600000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.616</v>
+        <v>0.37832</v>
       </c>
       <c r="K5" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.418</v>
+        <v>0.41762</v>
       </c>
     </row>
   </sheetData>
@@ -1781,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1807,70 +1331,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -1883,55 +1372,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.66474</v>
       </c>
       <c r="C2" t="n">
-        <v>0.661</v>
+        <v>0.63115</v>
       </c>
       <c r="D2" t="n">
-        <v>0.737</v>
+        <v>0.71121</v>
       </c>
       <c r="E2" t="n">
-        <v>0.772</v>
+        <v>0.91675</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.89976</v>
       </c>
       <c r="G2" t="n">
-        <v>0.754</v>
+        <v>0.73928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9</v>
+        <v>0.5274</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.67492</v>
       </c>
       <c r="J2" t="n">
-        <v>0.739</v>
+        <v>0.58643</v>
       </c>
       <c r="K2" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.634</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.574</v>
+        <v>0.57361</v>
       </c>
     </row>
     <row r="3">
@@ -1941,55 +1409,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7</v>
+        <v>0.66796</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.66276</v>
       </c>
       <c r="D3" t="n">
-        <v>0.719</v>
+        <v>0.68305</v>
       </c>
       <c r="E3" t="n">
-        <v>0.789</v>
+        <v>0.90695</v>
       </c>
       <c r="F3" t="n">
-        <v>0.922</v>
+        <v>0.8894</v>
       </c>
       <c r="G3" t="n">
-        <v>0.769</v>
+        <v>0.78827</v>
       </c>
       <c r="H3" t="n">
-        <v>0.889</v>
+        <v>0.40837</v>
       </c>
       <c r="I3" t="n">
-        <v>0.733</v>
+        <v>0.65778</v>
       </c>
       <c r="J3" t="n">
-        <v>0.788</v>
+        <v>0.57339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.592</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.56754</v>
       </c>
     </row>
     <row r="4">
@@ -1999,55 +1446,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.681</v>
+        <v>0.64015</v>
       </c>
       <c r="C4" t="n">
-        <v>0.63</v>
+        <v>0.5773</v>
       </c>
       <c r="D4" t="n">
-        <v>0.744</v>
+        <v>0.72189</v>
       </c>
       <c r="E4" t="n">
-        <v>0.761</v>
+        <v>0.96028</v>
       </c>
       <c r="F4" t="n">
-        <v>0.96</v>
+        <v>0.91082</v>
       </c>
       <c r="G4" t="n">
-        <v>0.744</v>
+        <v>0.71189</v>
       </c>
       <c r="H4" t="n">
-        <v>0.911</v>
+        <v>0.52825</v>
       </c>
       <c r="I4" t="n">
-        <v>0.666</v>
+        <v>0.67492</v>
       </c>
       <c r="J4" t="n">
-        <v>0.712</v>
+        <v>0.59156</v>
       </c>
       <c r="K4" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.634</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.59</v>
+        <v>0.5904199999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2057,55 +1483,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.66994</v>
       </c>
       <c r="C5" t="n">
-        <v>0.658</v>
+        <v>0.64785</v>
       </c>
       <c r="D5" t="n">
-        <v>0.728</v>
+        <v>0.6983200000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.779</v>
+        <v>0.95736</v>
       </c>
       <c r="F5" t="n">
-        <v>0.953</v>
+        <v>0.90033</v>
       </c>
       <c r="G5" t="n">
-        <v>0.759</v>
+        <v>0.78377</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>0.40849</v>
       </c>
       <c r="I5" t="n">
-        <v>0.711</v>
+        <v>0.65778</v>
       </c>
       <c r="J5" t="n">
-        <v>0.784</v>
+        <v>0.57853</v>
       </c>
       <c r="K5" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.579</v>
+        <v>0.57881</v>
       </c>
     </row>
   </sheetData>
